--- a/artfynd/A 19387-2025 artfynd.xlsx
+++ b/artfynd/A 19387-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111253561</v>
+        <v>126424688</v>
       </c>
       <c r="B2" t="n">
-        <v>96236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>233</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bispgården, Jmt</t>
+          <t>Kälmyrriset, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588870.1632531353</v>
+        <v>588806</v>
       </c>
       <c r="R2" t="n">
-        <v>6986052.616044191</v>
+        <v>6985968</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,27 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-05</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>barrblandskog</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,555 +764,21 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Fältskikt med ris och mossa. Öppen ljus skog. Fattigt.</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elina Larsson</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elina Larsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Inventering av norna</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>111253558</v>
-      </c>
-      <c r="B3" t="n">
-        <v>96236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>233</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Norna</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Calypso bulbosa</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) Oakes</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Bispgården, Jmt</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>588586.3818966502</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6986023.058864191</v>
-      </c>
-      <c r="S3" t="n">
-        <v>50</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Fors</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2023-05-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2023-05-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>sumptallskog</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Risdominerat.  Lingon och kråkbär dominerar.</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Elina Larsson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Elina Larsson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Inventering av norna</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>111253559</v>
-      </c>
-      <c r="B4" t="n">
-        <v>96236</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>233</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Norna</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Calypso bulbosa</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(L.) Oakes</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Bispgården, Jmt</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>588697.8232670003</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6986010.631868768</v>
-      </c>
-      <c r="S4" t="n">
-        <v>50</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Fors</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2023-05-25</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2023-05-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>sumptallskog</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Risdominerat fältskikt men även mossa. Öppen skog. Kråkbär, starr, vitmossa,  lingon. Med dike, troligen halvt misslyckat försök till att dika ur tidigare myr.</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Elina Larsson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Elina Larsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Inventering av norna</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>111253557</v>
-      </c>
-      <c r="B5" t="n">
-        <v>96236</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>233</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Norna</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Calypso bulbosa</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(L.) Oakes</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Bispgården, Jmt</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>588496.5487820518</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6986027.89194785</v>
-      </c>
-      <c r="S5" t="n">
-        <v>50</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Fors</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2023-05-25</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2023-05-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>sumptallskog</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Starrdominerat.  Glesare mellan tallarna, närmar sig myr. Mer starr. Vitmossa, dvärgbjörk, rosling.</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Elina Larsson</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Elina Larsson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Inventering av norna</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>111253560</v>
-      </c>
-      <c r="B6" t="n">
-        <v>96236</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>233</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Norna</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Calypso bulbosa</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) Oakes</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Bispgården, Jmt</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>588743.5063492842</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6986021.879939866</v>
-      </c>
-      <c r="S6" t="n">
-        <v>50</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Ragunda</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Fors</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2023-05-25</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2023-05-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>sumptallskog</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Risdominerat fältskikt. Öppen skog. Vitmossa, ljung, starr, blåbär, lingon.</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Elina Larsson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Elina Larsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>Inventering av norna</t>
-        </is>
-      </c>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19387-2025 artfynd.xlsx
+++ b/artfynd/A 19387-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,8 +784,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126424688</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>